--- a/ComponentesMetodologicos/Normalizacion.xlsx
+++ b/ComponentesMetodologicos/Normalizacion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrador\Desktop\Proyecto JEPL\PROYECTO_CEREBRUM\PROYECTO_CEREBRUM\ComponentesMetodologicos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8089D4A-FD02-4327-8293-C86B702D1EB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{537DA07F-40F7-4643-A2A1-5B155FFC5D37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,12 +28,12 @@
   </definedNames>
   <calcPr calcId="0"/>
   <customWorkbookViews>
+    <customWorkbookView name="Tabla2 filter view" guid="{E35139AA-24E9-4A62-81CA-588D087135E4}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Tabla4 filter view" guid="{D65A4ACE-247C-439E-AEA8-2EA75470FCA5}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Tabla3 filter view" guid="{7812FD8C-0E59-45E2-87A2-7698E6BE27A1}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Tabla11 filter view" guid="{5BA99981-AF65-4323-B2F8-5F691FA1504F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Tabla1 filter view" guid="{4BE0AE49-5167-486F-A74B-07AF5BFCAA2A}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
     <customWorkbookView name="Tabla5 filter view" guid="{626D8D2F-B7BD-49F0-B146-21AFFE642FF9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Tabla1 filter view" guid="{4BE0AE49-5167-486F-A74B-07AF5BFCAA2A}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Tabla11 filter view" guid="{5BA99981-AF65-4323-B2F8-5F691FA1504F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Tabla3 filter view" guid="{7812FD8C-0E59-45E2-87A2-7698E6BE27A1}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Tabla4 filter view" guid="{D65A4ACE-247C-439E-AEA8-2EA75470FCA5}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Tabla2 filter view" guid="{E35139AA-24E9-4A62-81CA-588D087135E4}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
   </customWorkbookViews>
   <extLst>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -3722,30 +3722,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="23" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3785,11 +3765,28 @@
     <xf numFmtId="0" fontId="3" fillId="22" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="17" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3800,6 +3797,9 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="22" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -36432,33 +36432,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A1" s="199" t="s">
+      <c r="A1" s="193" t="s">
         <v>688</v>
       </c>
-      <c r="B1" s="200"/>
-      <c r="C1" s="200"/>
-      <c r="D1" s="200"/>
-      <c r="E1" s="200"/>
-      <c r="F1" s="200"/>
-      <c r="G1" s="200"/>
-      <c r="H1" s="201"/>
-      <c r="N1" s="191" t="s">
+      <c r="B1" s="194"/>
+      <c r="C1" s="194"/>
+      <c r="D1" s="194"/>
+      <c r="E1" s="194"/>
+      <c r="F1" s="194"/>
+      <c r="G1" s="194"/>
+      <c r="H1" s="195"/>
+      <c r="N1" s="206" t="s">
         <v>10</v>
       </c>
-      <c r="O1" s="192"/>
-      <c r="P1" s="193"/>
-      <c r="R1" s="194" t="s">
+      <c r="O1" s="207"/>
+      <c r="P1" s="208"/>
+      <c r="R1" s="209" t="s">
         <v>417</v>
       </c>
-      <c r="S1" s="194"/>
-      <c r="T1" s="194"/>
-      <c r="V1" s="188" t="s">
+      <c r="S1" s="209"/>
+      <c r="T1" s="209"/>
+      <c r="V1" s="203" t="s">
         <v>418</v>
       </c>
-      <c r="W1" s="189"/>
-      <c r="X1" s="189"/>
-      <c r="Y1" s="189"/>
-      <c r="Z1" s="190"/>
+      <c r="W1" s="204"/>
+      <c r="X1" s="204"/>
+      <c r="Y1" s="204"/>
+      <c r="Z1" s="205"/>
     </row>
     <row r="2" spans="1:26">
       <c r="A2" s="152" t="s">
@@ -36485,10 +36485,10 @@
       <c r="H2" s="152" t="s">
         <v>689</v>
       </c>
-      <c r="J2" s="202" t="s">
+      <c r="J2" s="196" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="203"/>
+      <c r="K2" s="197"/>
       <c r="N2" s="111" t="s">
         <v>549</v>
       </c>
@@ -36932,10 +36932,10 @@
       <c r="H9" s="159" t="s">
         <v>501</v>
       </c>
-      <c r="J9" s="204" t="s">
+      <c r="J9" s="198" t="s">
         <v>492</v>
       </c>
-      <c r="K9" s="205"/>
+      <c r="K9" s="199"/>
       <c r="N9" s="103" t="s">
         <v>589</v>
       </c>
@@ -37379,11 +37379,11 @@
       <c r="H16" s="159" t="s">
         <v>501</v>
       </c>
-      <c r="J16" s="206" t="s">
+      <c r="J16" s="200" t="s">
         <v>11</v>
       </c>
-      <c r="K16" s="207"/>
-      <c r="L16" s="208"/>
+      <c r="K16" s="201"/>
+      <c r="L16" s="202"/>
       <c r="N16" s="103" t="s">
         <v>632</v>
       </c>
@@ -37920,11 +37920,11 @@
       <c r="L24" s="103" t="s">
         <v>346</v>
       </c>
-      <c r="N24" s="191" t="s">
+      <c r="N24" s="206" t="s">
         <v>6</v>
       </c>
-      <c r="O24" s="192"/>
-      <c r="P24" s="193"/>
+      <c r="O24" s="207"/>
+      <c r="P24" s="208"/>
       <c r="R24" s="39" t="s">
         <v>560</v>
       </c>
@@ -39004,10 +39004,10 @@
       <c r="P40" s="101" t="s">
         <v>373</v>
       </c>
-      <c r="R40" s="195" t="s">
+      <c r="R40" s="210" t="s">
         <v>419</v>
       </c>
-      <c r="S40" s="195"/>
+      <c r="S40" s="210"/>
       <c r="V40" s="140" t="s">
         <v>655</v>
       </c>
@@ -39300,11 +39300,11 @@
       <c r="H45" s="159" t="s">
         <v>507</v>
       </c>
-      <c r="J45" s="196" t="s">
+      <c r="J45" s="190" t="s">
         <v>534</v>
       </c>
-      <c r="K45" s="197"/>
-      <c r="L45" s="198"/>
+      <c r="K45" s="191"/>
+      <c r="L45" s="192"/>
       <c r="R45" s="105" t="s">
         <v>452</v>
       </c>
@@ -39361,10 +39361,10 @@
       <c r="L46" s="115" t="s">
         <v>541</v>
       </c>
-      <c r="N46" s="209" t="s">
+      <c r="N46" s="188" t="s">
         <v>408</v>
       </c>
-      <c r="O46" s="210"/>
+      <c r="O46" s="189"/>
       <c r="R46" s="105" t="s">
         <v>459</v>
       </c>
@@ -41096,73 +41096,73 @@
     <row r="999" ht="15.75" customHeight="1"/>
   </sheetData>
   <customSheetViews>
+    <customSheetView guid="{E35139AA-24E9-4A62-81CA-588D087135E4}" filter="1" showAutoFilter="1">
+      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+      <autoFilter ref="I80:K99" xr:uid="{1153904C-20BE-4AE7-9AA2-97435E0C38C8}"/>
+      <extLst>
+        <ext uri="GoogleSheetsCustomDataVersion1">
+          <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" filterViewId="1238617615"/>
+        </ext>
+      </extLst>
+    </customSheetView>
+    <customSheetView guid="{7812FD8C-0E59-45E2-87A2-7698E6BE27A1}" filter="1" showAutoFilter="1">
+      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+      <autoFilter ref="A53:G72" xr:uid="{8624AD03-2A6C-498F-89DD-162D19532C1D}"/>
+      <extLst>
+        <ext uri="GoogleSheetsCustomDataVersion1">
+          <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" filterViewId="1795137491"/>
+        </ext>
+      </extLst>
+    </customSheetView>
+    <customSheetView guid="{5BA99981-AF65-4323-B2F8-5F691FA1504F}" filter="1" showAutoFilter="1">
+      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+      <autoFilter ref="U55:Y104" xr:uid="{19A30CFB-B537-4404-9028-A6B9C3D1B6FB}"/>
+      <extLst>
+        <ext uri="GoogleSheetsCustomDataVersion1">
+          <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" filterViewId="2069367905"/>
+        </ext>
+      </extLst>
+    </customSheetView>
+    <customSheetView guid="{626D8D2F-B7BD-49F0-B146-21AFFE642FF9}" filter="1" showAutoFilter="1">
+      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+      <autoFilter ref="B80:C92" xr:uid="{39D1C793-E247-405D-80E7-B5337065EDBC}"/>
+      <extLst>
+        <ext uri="GoogleSheetsCustomDataVersion1">
+          <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" filterViewId="22588955"/>
+        </ext>
+      </extLst>
+    </customSheetView>
+    <customSheetView guid="{D65A4ACE-247C-439E-AEA8-2EA75470FCA5}" filter="1" showAutoFilter="1">
+      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+      <autoFilter ref="K53:L57" xr:uid="{8C8C0184-8170-4DE6-9D02-EC15D00C47ED}"/>
+      <extLst>
+        <ext uri="GoogleSheetsCustomDataVersion1">
+          <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" filterViewId="60796271"/>
+        </ext>
+      </extLst>
+    </customSheetView>
     <customSheetView guid="{4BE0AE49-5167-486F-A74B-07AF5BFCAA2A}" filter="1" showAutoFilter="1">
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="E80:G99" xr:uid="{F65CFEB8-6B68-4109-84A2-4441358A7D71}"/>
+      <autoFilter ref="E80:G99" xr:uid="{E1571859-14A4-450F-B02F-E7D88EC7FE10}"/>
       <extLst>
         <ext uri="GoogleSheetsCustomDataVersion1">
           <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" filterViewId="769624659"/>
         </ext>
       </extLst>
     </customSheetView>
-    <customSheetView guid="{D65A4ACE-247C-439E-AEA8-2EA75470FCA5}" filter="1" showAutoFilter="1">
-      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="K53:L57" xr:uid="{4C770E63-15AE-4B57-A2E5-C85EEC4052FC}"/>
-      <extLst>
-        <ext uri="GoogleSheetsCustomDataVersion1">
-          <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" filterViewId="60796271"/>
-        </ext>
-      </extLst>
-    </customSheetView>
-    <customSheetView guid="{626D8D2F-B7BD-49F0-B146-21AFFE642FF9}" filter="1" showAutoFilter="1">
-      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="B80:C92" xr:uid="{060121E8-5ABA-4D0C-98A0-68A24F7D3D63}"/>
-      <extLst>
-        <ext uri="GoogleSheetsCustomDataVersion1">
-          <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" filterViewId="22588955"/>
-        </ext>
-      </extLst>
-    </customSheetView>
-    <customSheetView guid="{5BA99981-AF65-4323-B2F8-5F691FA1504F}" filter="1" showAutoFilter="1">
-      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="U55:Y104" xr:uid="{95D44E9C-61E6-4373-A1B7-2C59A995F4F6}"/>
-      <extLst>
-        <ext uri="GoogleSheetsCustomDataVersion1">
-          <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" filterViewId="2069367905"/>
-        </ext>
-      </extLst>
-    </customSheetView>
-    <customSheetView guid="{7812FD8C-0E59-45E2-87A2-7698E6BE27A1}" filter="1" showAutoFilter="1">
-      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="A53:G72" xr:uid="{EE4BBFC3-B95A-4D4F-B33E-E0AE8E4BADA0}"/>
-      <extLst>
-        <ext uri="GoogleSheetsCustomDataVersion1">
-          <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" filterViewId="1795137491"/>
-        </ext>
-      </extLst>
-    </customSheetView>
-    <customSheetView guid="{E35139AA-24E9-4A62-81CA-588D087135E4}" filter="1" showAutoFilter="1">
-      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="I80:K99" xr:uid="{2EC12B49-6739-4805-BF7B-9315666020B6}"/>
-      <extLst>
-        <ext uri="GoogleSheetsCustomDataVersion1">
-          <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" filterViewId="1238617615"/>
-        </ext>
-      </extLst>
-    </customSheetView>
   </customSheetViews>
   <mergeCells count="11">
+    <mergeCell ref="V1:Z1"/>
+    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="N1:P1"/>
+    <mergeCell ref="R1:T1"/>
+    <mergeCell ref="R40:S40"/>
     <mergeCell ref="N46:O46"/>
     <mergeCell ref="J45:L45"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="J2:K2"/>
     <mergeCell ref="J9:K9"/>
     <mergeCell ref="J16:L16"/>
-    <mergeCell ref="V1:Z1"/>
-    <mergeCell ref="N24:P24"/>
-    <mergeCell ref="N1:P1"/>
-    <mergeCell ref="R1:T1"/>
-    <mergeCell ref="R40:S40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -41204,36 +41204,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1">
-      <c r="A1" s="212" t="s">
+      <c r="A1" s="211" t="s">
         <v>688</v>
       </c>
-      <c r="B1" s="212"/>
-      <c r="C1" s="212"/>
-      <c r="D1" s="212"/>
+      <c r="B1" s="211"/>
+      <c r="C1" s="211"/>
+      <c r="D1" s="211"/>
       <c r="E1" s="154"/>
-      <c r="F1" s="196" t="s">
+      <c r="F1" s="190" t="s">
         <v>534</v>
       </c>
-      <c r="G1" s="197"/>
+      <c r="G1" s="191"/>
       <c r="H1" s="154"/>
-      <c r="J1" s="213" t="s">
+      <c r="J1" s="212" t="s">
         <v>11</v>
       </c>
-      <c r="K1" s="214"/>
-      <c r="N1" s="191" t="s">
+      <c r="K1" s="213"/>
+      <c r="N1" s="206" t="s">
         <v>10</v>
       </c>
-      <c r="O1" s="192"/>
+      <c r="O1" s="207"/>
       <c r="P1" s="169"/>
-      <c r="R1" s="202" t="s">
+      <c r="R1" s="196" t="s">
         <v>9</v>
       </c>
-      <c r="S1" s="203"/>
+      <c r="S1" s="197"/>
       <c r="T1" s="185"/>
-      <c r="U1" s="195" t="s">
+      <c r="U1" s="210" t="s">
         <v>419</v>
       </c>
-      <c r="V1" s="195"/>
+      <c r="V1" s="210"/>
       <c r="Z1" s="153"/>
     </row>
     <row r="2" spans="1:26">
@@ -41537,10 +41537,10 @@
         <v>501</v>
       </c>
       <c r="P8" s="167"/>
-      <c r="R8" s="204" t="s">
+      <c r="R8" s="198" t="s">
         <v>492</v>
       </c>
-      <c r="S8" s="205"/>
+      <c r="S8" s="199"/>
       <c r="T8" s="184"/>
       <c r="U8" s="105" t="s">
         <v>465</v>
@@ -41851,10 +41851,10 @@
         <v>512</v>
       </c>
       <c r="P15" s="167"/>
-      <c r="R15" s="209" t="s">
+      <c r="R15" s="188" t="s">
         <v>408</v>
       </c>
-      <c r="S15" s="210"/>
+      <c r="S15" s="189"/>
       <c r="T15" s="184"/>
       <c r="U15" s="105" t="s">
         <v>506</v>
@@ -42200,10 +42200,10 @@
       <c r="D23" s="159" t="s">
         <v>501</v>
       </c>
-      <c r="F23" s="191" t="s">
+      <c r="F23" s="206" t="s">
         <v>6</v>
       </c>
-      <c r="G23" s="192"/>
+      <c r="G23" s="207"/>
       <c r="J23" s="103" t="s">
         <v>598</v>
       </c>
@@ -42252,10 +42252,10 @@
         <v>653</v>
       </c>
       <c r="L24" s="179"/>
-      <c r="N24" s="211" t="s">
+      <c r="N24" s="214" t="s">
         <v>417</v>
       </c>
-      <c r="O24" s="211"/>
+      <c r="O24" s="214"/>
       <c r="P24" s="168"/>
       <c r="R24" s="122" t="s">
         <v>460</v>
@@ -42513,12 +42513,12 @@
       <c r="G30" s="101" t="s">
         <v>234</v>
       </c>
-      <c r="I30" s="188" t="s">
+      <c r="I30" s="203" t="s">
         <v>418</v>
       </c>
-      <c r="J30" s="189"/>
-      <c r="K30" s="189"/>
-      <c r="L30" s="189"/>
+      <c r="J30" s="204"/>
+      <c r="K30" s="204"/>
+      <c r="L30" s="204"/>
       <c r="N30" s="183" t="s">
         <v>455</v>
       </c>
@@ -43904,17 +43904,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="I30:L30"/>
+    <mergeCell ref="N24:O24"/>
+    <mergeCell ref="U1:V1"/>
+    <mergeCell ref="R15:S15"/>
+    <mergeCell ref="N1:O1"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="F23:G23"/>
     <mergeCell ref="R1:S1"/>
     <mergeCell ref="R8:S8"/>
     <mergeCell ref="J1:K1"/>
-    <mergeCell ref="I30:L30"/>
-    <mergeCell ref="N24:O24"/>
-    <mergeCell ref="U1:V1"/>
-    <mergeCell ref="R15:S15"/>
-    <mergeCell ref="N1:O1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
